--- a/output/2026-10-07_03_Serbia_Mačvanski_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-10-07_03_Serbia_Mačvanski_Depolverazione_Trattamento_aria.xlsx
@@ -484,7 +484,6 @@
           <t>+381 15 68 06 06</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Sede fisica confermata: Ćirila i Metodija 15, 15000 Šabac. Esistenza e settore confermati sia dal sito ufficiale (technology.bibus.com/rs-sr/) sia dalla pagina partner Filtration Group Industrial (industrial.filtrationgroup.com/locations/bibus-industry-doo/). Contatto aggiuntivo riportato: Jelena Škoro, tel. mobile +381 60/60 60 571 (fonte: pagina partner Filtration Group). Email non riportata: sui due siti consultati il campo email risultava offuscato/non leggibile (placeholder anti-spam), quindi non verificabile con certezza e lasciata vuota per non inventare dati.</t>
@@ -492,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
